--- a/artfynd/A 50826-2023 artfynd.xlsx
+++ b/artfynd/A 50826-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50826-2023 artfynd.xlsx
+++ b/artfynd/A 50826-2023 artfynd.xlsx
@@ -2047,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119787425</v>
+        <v>119787104</v>
       </c>
       <c r="B15" t="n">
-        <v>89230</v>
+        <v>91821</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1596</v>
+        <v>6055</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564783</v>
+        <v>564767</v>
       </c>
       <c r="R15" t="n">
-        <v>6968906</v>
+        <v>6968890</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119787104</v>
+        <v>119786557</v>
       </c>
       <c r="B16" t="n">
-        <v>91821</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,38 +2161,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6055</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564767</v>
+        <v>564694</v>
       </c>
       <c r="R16" t="n">
-        <v>6968890</v>
+        <v>6968815</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119786557</v>
+        <v>119787425</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>89230</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,38 +2263,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1596</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564694</v>
+        <v>564783</v>
       </c>
       <c r="R17" t="n">
-        <v>6968815</v>
+        <v>6968906</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 50826-2023 artfynd.xlsx
+++ b/artfynd/A 50826-2023 artfynd.xlsx
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119788409</v>
+        <v>119788406</v>
       </c>
       <c r="B5" t="n">
-        <v>88153</v>
+        <v>86412</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,21 +1043,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4962</v>
+        <v>3690</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119786611</v>
+        <v>119787011</v>
       </c>
       <c r="B6" t="n">
-        <v>79567</v>
+        <v>95202</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,34 +1145,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564703</v>
+        <v>564706</v>
       </c>
       <c r="R6" t="n">
-        <v>6968818</v>
+        <v>6968896</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119786605</v>
+        <v>119787703</v>
       </c>
       <c r="B7" t="n">
-        <v>91334</v>
+        <v>91834</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,38 +1243,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>717</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564703</v>
+        <v>564690</v>
       </c>
       <c r="R7" t="n">
-        <v>6968818</v>
+        <v>6968887</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119787760</v>
+        <v>119788409</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>88153</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,38 +1345,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564690</v>
+        <v>564437</v>
       </c>
       <c r="R8" t="n">
-        <v>6968887</v>
+        <v>6968844</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119787781</v>
+        <v>119788007</v>
       </c>
       <c r="B9" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,38 +1447,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564690</v>
+        <v>564432</v>
       </c>
       <c r="R9" t="n">
-        <v>6968887</v>
+        <v>6968837</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119787032</v>
+        <v>119787425</v>
       </c>
       <c r="B10" t="n">
-        <v>91825</v>
+        <v>89230</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,25 +1549,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1968</v>
+        <v>1596</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564772</v>
+        <v>564783</v>
       </c>
       <c r="R10" t="n">
-        <v>6968903</v>
+        <v>6968906</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119787828</v>
+        <v>119786568</v>
       </c>
       <c r="B11" t="n">
-        <v>91852</v>
+        <v>79607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564458</v>
+        <v>564693</v>
       </c>
       <c r="R11" t="n">
-        <v>6968869</v>
+        <v>6968816</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119787011</v>
+        <v>119787104</v>
       </c>
       <c r="B12" t="n">
-        <v>95202</v>
+        <v>91821</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,25 +1753,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>6055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564706</v>
+        <v>564767</v>
       </c>
       <c r="R12" t="n">
-        <v>6968896</v>
+        <v>6968890</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119787440</v>
+        <v>119786607</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,34 +1859,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564783</v>
+        <v>564703</v>
       </c>
       <c r="R13" t="n">
-        <v>6968905</v>
+        <v>6968818</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119787703</v>
+        <v>119786761</v>
       </c>
       <c r="B14" t="n">
-        <v>91834</v>
+        <v>57463</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1961,21 +1961,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564690</v>
+        <v>564701</v>
       </c>
       <c r="R14" t="n">
-        <v>6968887</v>
+        <v>6968836</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119787104</v>
+        <v>119787440</v>
       </c>
       <c r="B15" t="n">
-        <v>91821</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,25 +2059,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6055</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564767</v>
+        <v>564783</v>
       </c>
       <c r="R15" t="n">
-        <v>6968890</v>
+        <v>6968905</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119787425</v>
+        <v>119787032</v>
       </c>
       <c r="B17" t="n">
-        <v>89230</v>
+        <v>91825</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,25 +2263,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1596</v>
+        <v>1968</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564783</v>
+        <v>564772</v>
       </c>
       <c r="R17" t="n">
-        <v>6968906</v>
+        <v>6968903</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119788406</v>
+        <v>119787760</v>
       </c>
       <c r="B18" t="n">
-        <v>86412</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,38 +2365,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564437</v>
+        <v>564690</v>
       </c>
       <c r="R18" t="n">
-        <v>6968844</v>
+        <v>6968887</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119786607</v>
+        <v>119786605</v>
       </c>
       <c r="B20" t="n">
-        <v>79607</v>
+        <v>91334</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2569,25 +2569,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>717</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119788007</v>
+        <v>119787828</v>
       </c>
       <c r="B21" t="n">
-        <v>89275</v>
+        <v>91852</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2671,25 +2671,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6286</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564432</v>
+        <v>564458</v>
       </c>
       <c r="R21" t="n">
-        <v>6968837</v>
+        <v>6968869</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119786568</v>
+        <v>119786611</v>
       </c>
       <c r="B22" t="n">
-        <v>79607</v>
+        <v>79567</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2773,25 +2773,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564693</v>
+        <v>564703</v>
       </c>
       <c r="R22" t="n">
-        <v>6968816</v>
+        <v>6968818</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119786761</v>
+        <v>119787781</v>
       </c>
       <c r="B23" t="n">
-        <v>57463</v>
+        <v>91884</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2879,21 +2879,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564701</v>
+        <v>564690</v>
       </c>
       <c r="R23" t="n">
-        <v>6968836</v>
+        <v>6968887</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 50826-2023 artfynd.xlsx
+++ b/artfynd/A 50826-2023 artfynd.xlsx
@@ -2047,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119787440</v>
+        <v>119787032</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>91825</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1968</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564783</v>
+        <v>564772</v>
       </c>
       <c r="R15" t="n">
-        <v>6968905</v>
+        <v>6968903</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119786557</v>
+        <v>119787440</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2165,34 +2165,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564694</v>
+        <v>564783</v>
       </c>
       <c r="R16" t="n">
-        <v>6968815</v>
+        <v>6968905</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119787032</v>
+        <v>119786557</v>
       </c>
       <c r="B17" t="n">
-        <v>91825</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2267,34 +2267,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1968</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564772</v>
+        <v>564694</v>
       </c>
       <c r="R17" t="n">
-        <v>6968903</v>
+        <v>6968815</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 50826-2023 artfynd.xlsx
+++ b/artfynd/A 50826-2023 artfynd.xlsx
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119788406</v>
+        <v>119787032</v>
       </c>
       <c r="B5" t="n">
-        <v>86412</v>
+        <v>91825</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,34 +1043,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3690</v>
+        <v>1968</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564437</v>
+        <v>564772</v>
       </c>
       <c r="R5" t="n">
-        <v>6968844</v>
+        <v>6968903</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1231,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119787703</v>
+        <v>119788007</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>89275</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,38 +1243,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>6286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564690</v>
+        <v>564432</v>
       </c>
       <c r="R7" t="n">
-        <v>6968887</v>
+        <v>6968837</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119788409</v>
+        <v>119787104</v>
       </c>
       <c r="B8" t="n">
-        <v>88153</v>
+        <v>91821</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,38 +1345,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4962</v>
+        <v>6055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564437</v>
+        <v>564767</v>
       </c>
       <c r="R8" t="n">
-        <v>6968844</v>
+        <v>6968890</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119788007</v>
+        <v>119786868</v>
       </c>
       <c r="B9" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,38 +1447,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564432</v>
+        <v>564708</v>
       </c>
       <c r="R9" t="n">
-        <v>6968837</v>
+        <v>6968890</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119787425</v>
+        <v>119786761</v>
       </c>
       <c r="B10" t="n">
-        <v>89230</v>
+        <v>57463</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,25 +1549,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1596</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564783</v>
+        <v>564701</v>
       </c>
       <c r="R10" t="n">
-        <v>6968906</v>
+        <v>6968836</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119786568</v>
+        <v>119787703</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
+        <v>91834</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,34 +1655,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564693</v>
+        <v>564690</v>
       </c>
       <c r="R11" t="n">
-        <v>6968816</v>
+        <v>6968887</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119787104</v>
+        <v>119786605</v>
       </c>
       <c r="B12" t="n">
-        <v>91821</v>
+        <v>91334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,34 +1757,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6055</v>
+        <v>717</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564767</v>
+        <v>564703</v>
       </c>
       <c r="R12" t="n">
-        <v>6968890</v>
+        <v>6968818</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119786607</v>
+        <v>119786557</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564703</v>
+        <v>564694</v>
       </c>
       <c r="R13" t="n">
-        <v>6968818</v>
+        <v>6968815</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119786761</v>
+        <v>119787425</v>
       </c>
       <c r="B14" t="n">
-        <v>57463</v>
+        <v>89230</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,25 +1957,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>1596</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564701</v>
+        <v>564783</v>
       </c>
       <c r="R14" t="n">
-        <v>6968836</v>
+        <v>6968906</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119787032</v>
+        <v>119788406</v>
       </c>
       <c r="B15" t="n">
-        <v>91825</v>
+        <v>86412</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2063,34 +2063,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1968</v>
+        <v>3690</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564772</v>
+        <v>564437</v>
       </c>
       <c r="R15" t="n">
-        <v>6968903</v>
+        <v>6968844</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119787440</v>
+        <v>119786607</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2165,34 +2165,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564783</v>
+        <v>564703</v>
       </c>
       <c r="R16" t="n">
-        <v>6968905</v>
+        <v>6968818</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119786557</v>
+        <v>119786611</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>79567</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,25 +2263,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564694</v>
+        <v>564703</v>
       </c>
       <c r="R17" t="n">
-        <v>6968815</v>
+        <v>6968818</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119787760</v>
+        <v>119786568</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,38 +2365,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564690</v>
+        <v>564693</v>
       </c>
       <c r="R18" t="n">
-        <v>6968887</v>
+        <v>6968816</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,7 +2455,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119786868</v>
+        <v>119787760</v>
       </c>
       <c r="B19" t="n">
         <v>91840</v>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564708</v>
+        <v>564690</v>
       </c>
       <c r="R19" t="n">
-        <v>6968890</v>
+        <v>6968887</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119786605</v>
+        <v>119787781</v>
       </c>
       <c r="B20" t="n">
-        <v>91334</v>
+        <v>91884</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2569,38 +2569,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>717</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564703</v>
+        <v>564690</v>
       </c>
       <c r="R20" t="n">
-        <v>6968818</v>
+        <v>6968887</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119787828</v>
+        <v>119788409</v>
       </c>
       <c r="B21" t="n">
-        <v>91852</v>
+        <v>88153</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2671,25 +2671,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4366</v>
+        <v>4962</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564458</v>
+        <v>564437</v>
       </c>
       <c r="R21" t="n">
-        <v>6968869</v>
+        <v>6968844</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119786611</v>
+        <v>119787440</v>
       </c>
       <c r="B22" t="n">
-        <v>79567</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2773,38 +2773,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564703</v>
+        <v>564783</v>
       </c>
       <c r="R22" t="n">
-        <v>6968818</v>
+        <v>6968905</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119787781</v>
+        <v>119787828</v>
       </c>
       <c r="B23" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2875,38 +2875,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564690</v>
+        <v>564458</v>
       </c>
       <c r="R23" t="n">
-        <v>6968887</v>
+        <v>6968869</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 50826-2023 artfynd.xlsx
+++ b/artfynd/A 50826-2023 artfynd.xlsx
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119787032</v>
+        <v>119787703</v>
       </c>
       <c r="B5" t="n">
-        <v>91825</v>
+        <v>91834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,21 +1043,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564772</v>
+        <v>564690</v>
       </c>
       <c r="R5" t="n">
-        <v>6968903</v>
+        <v>6968887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119787011</v>
+        <v>119787440</v>
       </c>
       <c r="B6" t="n">
-        <v>95202</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,25 +1141,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564706</v>
+        <v>564783</v>
       </c>
       <c r="R6" t="n">
-        <v>6968896</v>
+        <v>6968905</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1333,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119787104</v>
+        <v>119786868</v>
       </c>
       <c r="B8" t="n">
-        <v>91821</v>
+        <v>91840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,25 +1345,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564767</v>
+        <v>564708</v>
       </c>
       <c r="R8" t="n">
         <v>6968890</v>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119786868</v>
+        <v>119787011</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>95202</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,21 +1451,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564708</v>
+        <v>564706</v>
       </c>
       <c r="R9" t="n">
-        <v>6968890</v>
+        <v>6968896</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119786761</v>
+        <v>119788409</v>
       </c>
       <c r="B10" t="n">
-        <v>57463</v>
+        <v>88153</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,34 +1553,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>4962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564701</v>
+        <v>564437</v>
       </c>
       <c r="R10" t="n">
-        <v>6968836</v>
+        <v>6968844</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119787703</v>
+        <v>119787781</v>
       </c>
       <c r="B11" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119786605</v>
+        <v>119787032</v>
       </c>
       <c r="B12" t="n">
-        <v>91334</v>
+        <v>91825</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,38 +1753,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>717</v>
+        <v>1968</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564703</v>
+        <v>564772</v>
       </c>
       <c r="R12" t="n">
-        <v>6968818</v>
+        <v>6968903</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119786557</v>
+        <v>119788406</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>86412</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>3690</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564694</v>
+        <v>564437</v>
       </c>
       <c r="R13" t="n">
-        <v>6968815</v>
+        <v>6968844</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119787425</v>
+        <v>119786557</v>
       </c>
       <c r="B14" t="n">
-        <v>89230</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,38 +1957,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1596</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564783</v>
+        <v>564694</v>
       </c>
       <c r="R14" t="n">
-        <v>6968906</v>
+        <v>6968815</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119788406</v>
+        <v>119786611</v>
       </c>
       <c r="B15" t="n">
-        <v>86412</v>
+        <v>79567</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,25 +2059,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3690</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564437</v>
+        <v>564703</v>
       </c>
       <c r="R15" t="n">
-        <v>6968844</v>
+        <v>6968818</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,7 +2149,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119786607</v>
+        <v>119786568</v>
       </c>
       <c r="B16" t="n">
         <v>79607</v>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564703</v>
+        <v>564693</v>
       </c>
       <c r="R16" t="n">
-        <v>6968818</v>
+        <v>6968816</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119786611</v>
+        <v>119786761</v>
       </c>
       <c r="B17" t="n">
-        <v>79567</v>
+        <v>57463</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,38 +2263,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564703</v>
+        <v>564701</v>
       </c>
       <c r="R17" t="n">
-        <v>6968818</v>
+        <v>6968836</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119786568</v>
+        <v>119786605</v>
       </c>
       <c r="B18" t="n">
-        <v>79607</v>
+        <v>91334</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,25 +2365,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>717</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564693</v>
+        <v>564703</v>
       </c>
       <c r="R18" t="n">
-        <v>6968816</v>
+        <v>6968818</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119787781</v>
+        <v>119787828</v>
       </c>
       <c r="B20" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2569,38 +2569,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564690</v>
+        <v>564458</v>
       </c>
       <c r="R20" t="n">
-        <v>6968887</v>
+        <v>6968869</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119788409</v>
+        <v>119786607</v>
       </c>
       <c r="B21" t="n">
-        <v>88153</v>
+        <v>79607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,21 +2675,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4962</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564437</v>
+        <v>564703</v>
       </c>
       <c r="R21" t="n">
-        <v>6968844</v>
+        <v>6968818</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119787440</v>
+        <v>119787425</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>89230</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2773,25 +2773,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1596</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2804,7 +2804,7 @@
         <v>564783</v>
       </c>
       <c r="R22" t="n">
-        <v>6968905</v>
+        <v>6968906</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119787828</v>
+        <v>119787104</v>
       </c>
       <c r="B23" t="n">
-        <v>91852</v>
+        <v>91821</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2875,38 +2875,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>6055</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564458</v>
+        <v>564767</v>
       </c>
       <c r="R23" t="n">
-        <v>6968869</v>
+        <v>6968890</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 50826-2023 artfynd.xlsx
+++ b/artfynd/A 50826-2023 artfynd.xlsx
@@ -2047,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119786611</v>
+        <v>119786568</v>
       </c>
       <c r="B15" t="n">
-        <v>79567</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,25 +2059,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564703</v>
+        <v>564693</v>
       </c>
       <c r="R15" t="n">
-        <v>6968818</v>
+        <v>6968816</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119786568</v>
+        <v>119786611</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
+        <v>79567</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,25 +2161,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564693</v>
+        <v>564703</v>
       </c>
       <c r="R16" t="n">
-        <v>6968816</v>
+        <v>6968818</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 50826-2023 artfynd.xlsx
+++ b/artfynd/A 50826-2023 artfynd.xlsx
@@ -2047,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119786568</v>
+        <v>119786611</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>79567</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,25 +2059,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564693</v>
+        <v>564703</v>
       </c>
       <c r="R15" t="n">
-        <v>6968816</v>
+        <v>6968818</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119786611</v>
+        <v>119786568</v>
       </c>
       <c r="B16" t="n">
-        <v>79567</v>
+        <v>79607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,25 +2161,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564703</v>
+        <v>564693</v>
       </c>
       <c r="R16" t="n">
-        <v>6968818</v>
+        <v>6968816</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2455,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119787760</v>
+        <v>119787828</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2471,34 +2471,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564690</v>
+        <v>564458</v>
       </c>
       <c r="R19" t="n">
-        <v>6968887</v>
+        <v>6968869</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119787828</v>
+        <v>119787760</v>
       </c>
       <c r="B20" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2573,34 +2573,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564458</v>
+        <v>564690</v>
       </c>
       <c r="R20" t="n">
-        <v>6968869</v>
+        <v>6968887</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 50826-2023 artfynd.xlsx
+++ b/artfynd/A 50826-2023 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>119787125</v>
       </c>
       <c r="B4" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119787703</v>
+        <v>119788409</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>88170</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,34 +1043,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564690</v>
+        <v>564437</v>
       </c>
       <c r="R5" t="n">
-        <v>6968887</v>
+        <v>6968844</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119787440</v>
+        <v>119787425</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>89247</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,25 +1141,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1596</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
         <v>564783</v>
       </c>
       <c r="R6" t="n">
-        <v>6968905</v>
+        <v>6968906</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119788007</v>
+        <v>119787781</v>
       </c>
       <c r="B7" t="n">
-        <v>89275</v>
+        <v>91902</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,38 +1243,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564432</v>
+        <v>564690</v>
       </c>
       <c r="R7" t="n">
-        <v>6968837</v>
+        <v>6968887</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119786868</v>
+        <v>119786761</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,25 +1345,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564708</v>
+        <v>564701</v>
       </c>
       <c r="R8" t="n">
-        <v>6968890</v>
+        <v>6968836</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119787011</v>
+        <v>119786605</v>
       </c>
       <c r="B9" t="n">
-        <v>95202</v>
+        <v>91352</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,38 +1447,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>717</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564706</v>
+        <v>564703</v>
       </c>
       <c r="R9" t="n">
-        <v>6968896</v>
+        <v>6968818</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119788409</v>
+        <v>119787760</v>
       </c>
       <c r="B10" t="n">
-        <v>88153</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,38 +1549,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564437</v>
+        <v>564690</v>
       </c>
       <c r="R10" t="n">
-        <v>6968844</v>
+        <v>6968887</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119787781</v>
+        <v>119786868</v>
       </c>
       <c r="B11" t="n">
-        <v>91884</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564690</v>
+        <v>564708</v>
       </c>
       <c r="R11" t="n">
-        <v>6968887</v>
+        <v>6968890</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119787032</v>
+        <v>119786607</v>
       </c>
       <c r="B12" t="n">
-        <v>91825</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,34 +1757,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1968</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564772</v>
+        <v>564703</v>
       </c>
       <c r="R12" t="n">
-        <v>6968903</v>
+        <v>6968818</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119788406</v>
+        <v>119787440</v>
       </c>
       <c r="B13" t="n">
-        <v>86412</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,34 +1859,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3690</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564437</v>
+        <v>564783</v>
       </c>
       <c r="R13" t="n">
-        <v>6968844</v>
+        <v>6968905</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119786557</v>
+        <v>119787828</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>91870</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,25 +1957,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564694</v>
+        <v>564458</v>
       </c>
       <c r="R14" t="n">
-        <v>6968815</v>
+        <v>6968869</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,7 +2050,7 @@
         <v>119786568</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119786611</v>
+        <v>119786557</v>
       </c>
       <c r="B16" t="n">
-        <v>79567</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,25 +2161,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564703</v>
+        <v>564694</v>
       </c>
       <c r="R16" t="n">
-        <v>6968818</v>
+        <v>6968815</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119786761</v>
+        <v>119787104</v>
       </c>
       <c r="B17" t="n">
-        <v>57463</v>
+        <v>91839</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,25 +2263,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6055</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564701</v>
+        <v>564767</v>
       </c>
       <c r="R17" t="n">
-        <v>6968836</v>
+        <v>6968890</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119786605</v>
+        <v>119787703</v>
       </c>
       <c r="B18" t="n">
-        <v>91334</v>
+        <v>91852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,38 +2365,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>717</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564703</v>
+        <v>564690</v>
       </c>
       <c r="R18" t="n">
-        <v>6968818</v>
+        <v>6968887</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119787828</v>
+        <v>119786611</v>
       </c>
       <c r="B19" t="n">
-        <v>91852</v>
+        <v>79583</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564458</v>
+        <v>564703</v>
       </c>
       <c r="R19" t="n">
-        <v>6968869</v>
+        <v>6968818</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119787760</v>
+        <v>119788007</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>89292</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2569,38 +2569,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564690</v>
+        <v>564432</v>
       </c>
       <c r="R20" t="n">
-        <v>6968887</v>
+        <v>6968837</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119786607</v>
+        <v>119787032</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>91843</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,34 +2675,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1968</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564703</v>
+        <v>564772</v>
       </c>
       <c r="R21" t="n">
-        <v>6968818</v>
+        <v>6968903</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119787425</v>
+        <v>119787011</v>
       </c>
       <c r="B22" t="n">
-        <v>89230</v>
+        <v>95225</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2773,25 +2773,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1596</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564783</v>
+        <v>564706</v>
       </c>
       <c r="R22" t="n">
-        <v>6968906</v>
+        <v>6968896</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119787104</v>
+        <v>119788406</v>
       </c>
       <c r="B23" t="n">
-        <v>91821</v>
+        <v>86429</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2875,38 +2875,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6055</v>
+        <v>3690</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564767</v>
+        <v>564437</v>
       </c>
       <c r="R23" t="n">
-        <v>6968890</v>
+        <v>6968844</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 50826-2023 artfynd.xlsx
+++ b/artfynd/A 50826-2023 artfynd.xlsx
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119786605</v>
+        <v>119786607</v>
       </c>
       <c r="B9" t="n">
-        <v>91352</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,25 +1447,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>717</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119786607</v>
+        <v>119786605</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>91352</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,25 +1753,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>717</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>

--- a/artfynd/A 50826-2023 artfynd.xlsx
+++ b/artfynd/A 50826-2023 artfynd.xlsx
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119788409</v>
+        <v>119787032</v>
       </c>
       <c r="B5" t="n">
-        <v>88170</v>
+        <v>91843</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,34 +1043,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4962</v>
+        <v>1968</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564437</v>
+        <v>564772</v>
       </c>
       <c r="R5" t="n">
-        <v>6968844</v>
+        <v>6968903</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119787425</v>
+        <v>119786611</v>
       </c>
       <c r="B6" t="n">
-        <v>89247</v>
+        <v>79583</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,38 +1141,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1596</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564783</v>
+        <v>564703</v>
       </c>
       <c r="R6" t="n">
-        <v>6968906</v>
+        <v>6968818</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119787781</v>
+        <v>119787440</v>
       </c>
       <c r="B7" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,21 +1247,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564690</v>
+        <v>564783</v>
       </c>
       <c r="R7" t="n">
-        <v>6968887</v>
+        <v>6968905</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119786761</v>
+        <v>119787703</v>
       </c>
       <c r="B8" t="n">
-        <v>57473</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,21 +1349,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564701</v>
+        <v>564690</v>
       </c>
       <c r="R8" t="n">
-        <v>6968836</v>
+        <v>6968887</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119786607</v>
+        <v>119788007</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>89292</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,25 +1447,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564703</v>
+        <v>564432</v>
       </c>
       <c r="R9" t="n">
-        <v>6968818</v>
+        <v>6968837</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119787760</v>
+        <v>119787425</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>89247</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,25 +1549,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1596</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564690</v>
+        <v>564783</v>
       </c>
       <c r="R10" t="n">
-        <v>6968887</v>
+        <v>6968906</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,7 +1639,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119786868</v>
+        <v>119787760</v>
       </c>
       <c r="B11" t="n">
         <v>91858</v>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564708</v>
+        <v>564690</v>
       </c>
       <c r="R11" t="n">
-        <v>6968890</v>
+        <v>6968887</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119786605</v>
+        <v>119786868</v>
       </c>
       <c r="B12" t="n">
-        <v>91352</v>
+        <v>91858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,38 +1753,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>717</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564703</v>
+        <v>564708</v>
       </c>
       <c r="R12" t="n">
-        <v>6968818</v>
+        <v>6968890</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119787440</v>
+        <v>119786607</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,34 +1859,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564783</v>
+        <v>564703</v>
       </c>
       <c r="R13" t="n">
-        <v>6968905</v>
+        <v>6968818</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119787828</v>
+        <v>119786557</v>
       </c>
       <c r="B14" t="n">
-        <v>91870</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,25 +1957,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564458</v>
+        <v>564694</v>
       </c>
       <c r="R14" t="n">
-        <v>6968869</v>
+        <v>6968815</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119786568</v>
+        <v>119787828</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>91870</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,25 +2059,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564693</v>
+        <v>564458</v>
       </c>
       <c r="R15" t="n">
-        <v>6968816</v>
+        <v>6968869</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119786557</v>
+        <v>119786568</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2165,21 +2165,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564694</v>
+        <v>564693</v>
       </c>
       <c r="R16" t="n">
-        <v>6968815</v>
+        <v>6968816</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119787104</v>
+        <v>119787011</v>
       </c>
       <c r="B17" t="n">
-        <v>91839</v>
+        <v>95225</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,25 +2263,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6055</v>
+        <v>2869</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564767</v>
+        <v>564706</v>
       </c>
       <c r="R17" t="n">
-        <v>6968890</v>
+        <v>6968896</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119787703</v>
+        <v>119788406</v>
       </c>
       <c r="B18" t="n">
-        <v>91852</v>
+        <v>86429</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2369,34 +2369,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564690</v>
+        <v>564437</v>
       </c>
       <c r="R18" t="n">
-        <v>6968887</v>
+        <v>6968844</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119786611</v>
+        <v>119787104</v>
       </c>
       <c r="B19" t="n">
-        <v>79583</v>
+        <v>91839</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,38 +2467,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>6055</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564703</v>
+        <v>564767</v>
       </c>
       <c r="R19" t="n">
-        <v>6968818</v>
+        <v>6968890</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119788007</v>
+        <v>119787781</v>
       </c>
       <c r="B20" t="n">
-        <v>89292</v>
+        <v>91902</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2569,38 +2569,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564432</v>
+        <v>564690</v>
       </c>
       <c r="R20" t="n">
-        <v>6968837</v>
+        <v>6968887</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119787032</v>
+        <v>119786605</v>
       </c>
       <c r="B21" t="n">
-        <v>91843</v>
+        <v>91352</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2671,38 +2671,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1968</v>
+        <v>717</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564772</v>
+        <v>564703</v>
       </c>
       <c r="R21" t="n">
-        <v>6968903</v>
+        <v>6968818</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119787011</v>
+        <v>119786761</v>
       </c>
       <c r="B22" t="n">
-        <v>95225</v>
+        <v>57473</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2773,25 +2773,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2869</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564706</v>
+        <v>564701</v>
       </c>
       <c r="R22" t="n">
-        <v>6968896</v>
+        <v>6968836</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119788406</v>
+        <v>119788409</v>
       </c>
       <c r="B23" t="n">
-        <v>86429</v>
+        <v>88170</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2879,21 +2879,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3690</v>
+        <v>4962</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>

--- a/artfynd/A 50826-2023 artfynd.xlsx
+++ b/artfynd/A 50826-2023 artfynd.xlsx
@@ -2353,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119788406</v>
+        <v>119787104</v>
       </c>
       <c r="B18" t="n">
-        <v>86429</v>
+        <v>91839</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,38 +2365,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3690</v>
+        <v>6055</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564437</v>
+        <v>564767</v>
       </c>
       <c r="R18" t="n">
-        <v>6968844</v>
+        <v>6968890</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119787104</v>
+        <v>119788406</v>
       </c>
       <c r="B19" t="n">
-        <v>91839</v>
+        <v>86429</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,38 +2467,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6055</v>
+        <v>3690</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564767</v>
+        <v>564437</v>
       </c>
       <c r="R19" t="n">
-        <v>6968890</v>
+        <v>6968844</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119787781</v>
+        <v>119786605</v>
       </c>
       <c r="B20" t="n">
-        <v>91902</v>
+        <v>91352</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2569,38 +2569,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>717</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564690</v>
+        <v>564703</v>
       </c>
       <c r="R20" t="n">
-        <v>6968887</v>
+        <v>6968818</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119786605</v>
+        <v>119787781</v>
       </c>
       <c r="B21" t="n">
-        <v>91352</v>
+        <v>91902</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2671,38 +2671,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>717</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564703</v>
+        <v>564690</v>
       </c>
       <c r="R21" t="n">
-        <v>6968818</v>
+        <v>6968887</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 50826-2023 artfynd.xlsx
+++ b/artfynd/A 50826-2023 artfynd.xlsx
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119787032</v>
+        <v>119786868</v>
       </c>
       <c r="B5" t="n">
-        <v>91843</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,25 +1039,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564772</v>
+        <v>564708</v>
       </c>
       <c r="R5" t="n">
-        <v>6968903</v>
+        <v>6968890</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119786611</v>
+        <v>119787011</v>
       </c>
       <c r="B6" t="n">
-        <v>79583</v>
+        <v>95225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,34 +1145,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564703</v>
+        <v>564706</v>
       </c>
       <c r="R6" t="n">
-        <v>6968818</v>
+        <v>6968896</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119787440</v>
+        <v>119786568</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,34 +1247,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564783</v>
+        <v>564693</v>
       </c>
       <c r="R7" t="n">
-        <v>6968905</v>
+        <v>6968816</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119787703</v>
+        <v>119786611</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>79583</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,38 +1345,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564690</v>
+        <v>564703</v>
       </c>
       <c r="R8" t="n">
-        <v>6968887</v>
+        <v>6968818</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119788007</v>
+        <v>119788406</v>
       </c>
       <c r="B9" t="n">
-        <v>89292</v>
+        <v>86429</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,25 +1447,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6286</v>
+        <v>3690</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564432</v>
+        <v>564437</v>
       </c>
       <c r="R9" t="n">
-        <v>6968837</v>
+        <v>6968844</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119787425</v>
+        <v>119787703</v>
       </c>
       <c r="B10" t="n">
-        <v>89247</v>
+        <v>91852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,25 +1549,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1596</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564783</v>
+        <v>564690</v>
       </c>
       <c r="R10" t="n">
-        <v>6968906</v>
+        <v>6968887</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119787760</v>
+        <v>119788007</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>89292</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,38 +1651,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564690</v>
+        <v>564432</v>
       </c>
       <c r="R11" t="n">
-        <v>6968887</v>
+        <v>6968837</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119786868</v>
+        <v>119787781</v>
       </c>
       <c r="B12" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,25 +1753,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564708</v>
+        <v>564690</v>
       </c>
       <c r="R12" t="n">
-        <v>6968890</v>
+        <v>6968887</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119786607</v>
+        <v>119786605</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>91352</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,25 +1855,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>717</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119786557</v>
+        <v>119787828</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>91870</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,25 +1957,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564694</v>
+        <v>564458</v>
       </c>
       <c r="R14" t="n">
-        <v>6968815</v>
+        <v>6968869</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119787828</v>
+        <v>119788409</v>
       </c>
       <c r="B15" t="n">
-        <v>91870</v>
+        <v>88170</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,25 +2059,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>4962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564458</v>
+        <v>564437</v>
       </c>
       <c r="R15" t="n">
-        <v>6968869</v>
+        <v>6968844</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119786568</v>
+        <v>119787440</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2165,34 +2165,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564693</v>
+        <v>564783</v>
       </c>
       <c r="R16" t="n">
-        <v>6968816</v>
+        <v>6968905</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119787011</v>
+        <v>119787032</v>
       </c>
       <c r="B17" t="n">
-        <v>95225</v>
+        <v>91843</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,25 +2263,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2869</v>
+        <v>1968</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564706</v>
+        <v>564772</v>
       </c>
       <c r="R17" t="n">
-        <v>6968896</v>
+        <v>6968903</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119787104</v>
+        <v>119787425</v>
       </c>
       <c r="B18" t="n">
-        <v>91839</v>
+        <v>89247</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6055</v>
+        <v>1596</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564767</v>
+        <v>564783</v>
       </c>
       <c r="R18" t="n">
-        <v>6968890</v>
+        <v>6968906</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119788406</v>
+        <v>119787104</v>
       </c>
       <c r="B19" t="n">
-        <v>86429</v>
+        <v>91839</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,38 +2467,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3690</v>
+        <v>6055</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564437</v>
+        <v>564767</v>
       </c>
       <c r="R19" t="n">
-        <v>6968844</v>
+        <v>6968890</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119786605</v>
+        <v>119786607</v>
       </c>
       <c r="B20" t="n">
-        <v>91352</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2569,25 +2569,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>717</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119787781</v>
+        <v>119786761</v>
       </c>
       <c r="B21" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,21 +2675,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564690</v>
+        <v>564701</v>
       </c>
       <c r="R21" t="n">
-        <v>6968887</v>
+        <v>6968836</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119786761</v>
+        <v>119786557</v>
       </c>
       <c r="B22" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2777,34 +2777,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564701</v>
+        <v>564694</v>
       </c>
       <c r="R22" t="n">
-        <v>6968836</v>
+        <v>6968815</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119788409</v>
+        <v>119787760</v>
       </c>
       <c r="B23" t="n">
-        <v>88170</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2875,38 +2875,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564437</v>
+        <v>564690</v>
       </c>
       <c r="R23" t="n">
-        <v>6968844</v>
+        <v>6968887</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 50826-2023 artfynd.xlsx
+++ b/artfynd/A 50826-2023 artfynd.xlsx
@@ -1231,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119786568</v>
+        <v>119786611</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>79583</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,25 +1243,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564693</v>
+        <v>564703</v>
       </c>
       <c r="R7" t="n">
-        <v>6968816</v>
+        <v>6968818</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119786611</v>
+        <v>119786568</v>
       </c>
       <c r="B8" t="n">
-        <v>79583</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,25 +1345,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564703</v>
+        <v>564693</v>
       </c>
       <c r="R8" t="n">
-        <v>6968818</v>
+        <v>6968816</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119786605</v>
+        <v>119787828</v>
       </c>
       <c r="B13" t="n">
-        <v>91352</v>
+        <v>91870</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,25 +1855,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>717</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564703</v>
+        <v>564458</v>
       </c>
       <c r="R13" t="n">
-        <v>6968818</v>
+        <v>6968869</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119787828</v>
+        <v>119786605</v>
       </c>
       <c r="B14" t="n">
-        <v>91870</v>
+        <v>91352</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,25 +1957,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>717</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564458</v>
+        <v>564703</v>
       </c>
       <c r="R14" t="n">
-        <v>6968869</v>
+        <v>6968818</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119786557</v>
+        <v>119787760</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2773,38 +2773,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564694</v>
+        <v>564690</v>
       </c>
       <c r="R22" t="n">
-        <v>6968815</v>
+        <v>6968887</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119787760</v>
+        <v>119786557</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2875,38 +2875,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564690</v>
+        <v>564694</v>
       </c>
       <c r="R23" t="n">
-        <v>6968887</v>
+        <v>6968815</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 50826-2023 artfynd.xlsx
+++ b/artfynd/A 50826-2023 artfynd.xlsx
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119786868</v>
+        <v>119786557</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,38 +1039,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564708</v>
+        <v>564694</v>
       </c>
       <c r="R5" t="n">
-        <v>6968890</v>
+        <v>6968815</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119787011</v>
+        <v>119787425</v>
       </c>
       <c r="B6" t="n">
-        <v>95225</v>
+        <v>89247</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,25 +1141,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>1596</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564706</v>
+        <v>564783</v>
       </c>
       <c r="R6" t="n">
-        <v>6968896</v>
+        <v>6968906</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119786611</v>
+        <v>119786761</v>
       </c>
       <c r="B7" t="n">
-        <v>79583</v>
+        <v>57473</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,38 +1243,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564703</v>
+        <v>564701</v>
       </c>
       <c r="R7" t="n">
-        <v>6968818</v>
+        <v>6968836</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119786568</v>
+        <v>119787781</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>91902</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,34 +1349,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564693</v>
+        <v>564690</v>
       </c>
       <c r="R8" t="n">
-        <v>6968816</v>
+        <v>6968887</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119788406</v>
+        <v>119786611</v>
       </c>
       <c r="B9" t="n">
-        <v>86429</v>
+        <v>79583</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,25 +1447,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3690</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564437</v>
+        <v>564703</v>
       </c>
       <c r="R9" t="n">
-        <v>6968844</v>
+        <v>6968818</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119788007</v>
+        <v>119787760</v>
       </c>
       <c r="B11" t="n">
-        <v>89292</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,38 +1651,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564432</v>
+        <v>564690</v>
       </c>
       <c r="R11" t="n">
-        <v>6968837</v>
+        <v>6968887</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119787781</v>
+        <v>119786568</v>
       </c>
       <c r="B12" t="n">
-        <v>91902</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,34 +1757,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564690</v>
+        <v>564693</v>
       </c>
       <c r="R12" t="n">
-        <v>6968887</v>
+        <v>6968816</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119787828</v>
+        <v>119786607</v>
       </c>
       <c r="B13" t="n">
-        <v>91870</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,25 +1855,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564458</v>
+        <v>564703</v>
       </c>
       <c r="R13" t="n">
-        <v>6968869</v>
+        <v>6968818</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119786605</v>
+        <v>119788007</v>
       </c>
       <c r="B14" t="n">
-        <v>91352</v>
+        <v>89292</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1961,21 +1961,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>717</v>
+        <v>6286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564703</v>
+        <v>564432</v>
       </c>
       <c r="R14" t="n">
-        <v>6968818</v>
+        <v>6968837</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119788409</v>
+        <v>119787011</v>
       </c>
       <c r="B15" t="n">
-        <v>88170</v>
+        <v>95225</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,38 +2059,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4962</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564437</v>
+        <v>564706</v>
       </c>
       <c r="R15" t="n">
-        <v>6968844</v>
+        <v>6968896</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119787440</v>
+        <v>119787828</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>91870</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,38 +2161,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564783</v>
+        <v>564458</v>
       </c>
       <c r="R16" t="n">
-        <v>6968905</v>
+        <v>6968869</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119787032</v>
+        <v>119786868</v>
       </c>
       <c r="B17" t="n">
-        <v>91843</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,25 +2263,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564772</v>
+        <v>564708</v>
       </c>
       <c r="R17" t="n">
-        <v>6968903</v>
+        <v>6968890</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119787425</v>
+        <v>119787032</v>
       </c>
       <c r="B18" t="n">
-        <v>89247</v>
+        <v>91843</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,25 +2365,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1596</v>
+        <v>1968</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564783</v>
+        <v>564772</v>
       </c>
       <c r="R18" t="n">
-        <v>6968906</v>
+        <v>6968903</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119787104</v>
+        <v>119788409</v>
       </c>
       <c r="B19" t="n">
-        <v>91839</v>
+        <v>88170</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,38 +2467,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6055</v>
+        <v>4962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564767</v>
+        <v>564437</v>
       </c>
       <c r="R19" t="n">
-        <v>6968890</v>
+        <v>6968844</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119786607</v>
+        <v>119786605</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>91352</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2569,25 +2569,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>717</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119786761</v>
+        <v>119787440</v>
       </c>
       <c r="B21" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,21 +2675,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564701</v>
+        <v>564783</v>
       </c>
       <c r="R21" t="n">
-        <v>6968836</v>
+        <v>6968905</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119787760</v>
+        <v>119788406</v>
       </c>
       <c r="B22" t="n">
-        <v>91858</v>
+        <v>86429</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2773,38 +2773,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564690</v>
+        <v>564437</v>
       </c>
       <c r="R22" t="n">
-        <v>6968887</v>
+        <v>6968844</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119786557</v>
+        <v>119787104</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>91839</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2875,38 +2875,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6055</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564694</v>
+        <v>564767</v>
       </c>
       <c r="R23" t="n">
-        <v>6968815</v>
+        <v>6968890</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 50826-2023 artfynd.xlsx
+++ b/artfynd/A 50826-2023 artfynd.xlsx
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119786557</v>
+        <v>119787781</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>91902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,34 +1043,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564694</v>
+        <v>564690</v>
       </c>
       <c r="R5" t="n">
-        <v>6968815</v>
+        <v>6968887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119787425</v>
+        <v>119788406</v>
       </c>
       <c r="B6" t="n">
-        <v>89247</v>
+        <v>86429</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,38 +1141,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1596</v>
+        <v>3690</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564783</v>
+        <v>564437</v>
       </c>
       <c r="R6" t="n">
-        <v>6968906</v>
+        <v>6968844</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119786761</v>
+        <v>119786611</v>
       </c>
       <c r="B7" t="n">
-        <v>57473</v>
+        <v>79583</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,38 +1243,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564701</v>
+        <v>564703</v>
       </c>
       <c r="R7" t="n">
-        <v>6968836</v>
+        <v>6968818</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119787781</v>
+        <v>119787032</v>
       </c>
       <c r="B8" t="n">
-        <v>91902</v>
+        <v>91843</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,21 +1349,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>1968</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564690</v>
+        <v>564772</v>
       </c>
       <c r="R8" t="n">
-        <v>6968887</v>
+        <v>6968903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119786611</v>
+        <v>119787828</v>
       </c>
       <c r="B9" t="n">
-        <v>79583</v>
+        <v>91870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,21 +1451,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564703</v>
+        <v>564458</v>
       </c>
       <c r="R9" t="n">
-        <v>6968818</v>
+        <v>6968869</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119787703</v>
+        <v>119786607</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,34 +1553,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564690</v>
+        <v>564703</v>
       </c>
       <c r="R10" t="n">
-        <v>6968887</v>
+        <v>6968818</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119787760</v>
+        <v>119788007</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>89292</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,38 +1651,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564690</v>
+        <v>564432</v>
       </c>
       <c r="R11" t="n">
-        <v>6968887</v>
+        <v>6968837</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119786568</v>
+        <v>119786605</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>91352</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,25 +1753,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>717</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564693</v>
+        <v>564703</v>
       </c>
       <c r="R12" t="n">
-        <v>6968816</v>
+        <v>6968818</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119786607</v>
+        <v>119787760</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,38 +1855,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564703</v>
+        <v>564690</v>
       </c>
       <c r="R13" t="n">
-        <v>6968818</v>
+        <v>6968887</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119788007</v>
+        <v>119786868</v>
       </c>
       <c r="B14" t="n">
-        <v>89292</v>
+        <v>91858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,38 +1957,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564432</v>
+        <v>564708</v>
       </c>
       <c r="R14" t="n">
-        <v>6968837</v>
+        <v>6968890</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119787828</v>
+        <v>119786761</v>
       </c>
       <c r="B16" t="n">
-        <v>91870</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,38 +2161,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564458</v>
+        <v>564701</v>
       </c>
       <c r="R16" t="n">
-        <v>6968869</v>
+        <v>6968836</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119786868</v>
+        <v>119788409</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>88170</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,38 +2263,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564708</v>
+        <v>564437</v>
       </c>
       <c r="R17" t="n">
-        <v>6968890</v>
+        <v>6968844</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119787032</v>
+        <v>119787440</v>
       </c>
       <c r="B18" t="n">
-        <v>91843</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1968</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564772</v>
+        <v>564783</v>
       </c>
       <c r="R18" t="n">
-        <v>6968903</v>
+        <v>6968905</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119788409</v>
+        <v>119786568</v>
       </c>
       <c r="B19" t="n">
-        <v>88170</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4962</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564437</v>
+        <v>564693</v>
       </c>
       <c r="R19" t="n">
-        <v>6968844</v>
+        <v>6968816</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119786605</v>
+        <v>119787703</v>
       </c>
       <c r="B20" t="n">
-        <v>91352</v>
+        <v>91852</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2569,38 +2569,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>717</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564703</v>
+        <v>564690</v>
       </c>
       <c r="R20" t="n">
-        <v>6968818</v>
+        <v>6968887</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119787440</v>
+        <v>119786557</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,34 +2675,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564783</v>
+        <v>564694</v>
       </c>
       <c r="R21" t="n">
-        <v>6968905</v>
+        <v>6968815</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119788406</v>
+        <v>119787425</v>
       </c>
       <c r="B22" t="n">
-        <v>86429</v>
+        <v>89247</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2773,38 +2773,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3690</v>
+        <v>1596</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564437</v>
+        <v>564783</v>
       </c>
       <c r="R22" t="n">
-        <v>6968844</v>
+        <v>6968906</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 50826-2023 artfynd.xlsx
+++ b/artfynd/A 50826-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17270547</v>
+        <v>119786605</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>717</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein. : Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norråmarkbodarna, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564612.4309927574</v>
+        <v>564703</v>
       </c>
       <c r="R2" t="n">
-        <v>6968842.173765619</v>
+        <v>6968818</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-10-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-10-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,82 +756,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17270580</v>
+        <v>119787425</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90674</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1596</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norråmarkbodarna, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564612.4309927574</v>
+        <v>564783</v>
       </c>
       <c r="R3" t="n">
-        <v>6968842.173765619</v>
+        <v>6968906</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-10-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-10-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,40 +853,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119787125</v>
+        <v>119787032</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>1968</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564780</v>
+        <v>564772</v>
       </c>
       <c r="R4" t="n">
-        <v>6968906</v>
+        <v>6968903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1027,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119787781</v>
+        <v>119787319</v>
       </c>
       <c r="B5" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1067,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564690</v>
+        <v>564807</v>
       </c>
       <c r="R5" t="n">
-        <v>6968887</v>
+        <v>6968923</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,50 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119788406</v>
+        <v>119787011</v>
       </c>
       <c r="B6" t="n">
-        <v>86429</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3690</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564437</v>
+        <v>564706</v>
       </c>
       <c r="R6" t="n">
-        <v>6968844</v>
+        <v>6968896</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119786611</v>
+        <v>119788406</v>
       </c>
       <c r="B7" t="n">
-        <v>79583</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>3690</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564703</v>
+        <v>564437</v>
       </c>
       <c r="R7" t="n">
-        <v>6968818</v>
+        <v>6968844</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119787032</v>
+        <v>119787125</v>
       </c>
       <c r="B8" t="n">
-        <v>91843</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1349,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1373,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564772</v>
+        <v>564780</v>
       </c>
       <c r="R8" t="n">
-        <v>6968903</v>
+        <v>6968906</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,50 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119787828</v>
+        <v>119787703</v>
       </c>
       <c r="B9" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564458</v>
+        <v>564690</v>
       </c>
       <c r="R9" t="n">
-        <v>6968869</v>
+        <v>6968887</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119786607</v>
+        <v>119786868</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564703</v>
+        <v>564708</v>
       </c>
       <c r="R10" t="n">
-        <v>6968818</v>
+        <v>6968890</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,50 +1548,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119788007</v>
+        <v>119787262</v>
       </c>
       <c r="B11" t="n">
-        <v>89292</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564432</v>
+        <v>564807</v>
       </c>
       <c r="R11" t="n">
-        <v>6968837</v>
+        <v>6968923</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,50 +1645,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119786605</v>
+        <v>119787760</v>
       </c>
       <c r="B12" t="n">
-        <v>91352</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>717</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564703</v>
+        <v>564690</v>
       </c>
       <c r="R12" t="n">
-        <v>6968818</v>
+        <v>6968887</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,50 +1742,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119787760</v>
+        <v>119787828</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564690</v>
+        <v>564458</v>
       </c>
       <c r="R13" t="n">
-        <v>6968887</v>
+        <v>6968869</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,50 +1839,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119786868</v>
+        <v>119788409</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564708</v>
+        <v>564437</v>
       </c>
       <c r="R14" t="n">
-        <v>6968890</v>
+        <v>6968844</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119787011</v>
+        <v>119787104</v>
       </c>
       <c r="B15" t="n">
-        <v>95225</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>6055</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564706</v>
+        <v>564767</v>
       </c>
       <c r="R15" t="n">
-        <v>6968896</v>
+        <v>6968890</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,50 +2033,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119786761</v>
+        <v>119788007</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564701</v>
+        <v>564432</v>
       </c>
       <c r="R16" t="n">
-        <v>6968836</v>
+        <v>6968837</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,50 +2130,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119788409</v>
+        <v>119787440</v>
       </c>
       <c r="B17" t="n">
-        <v>88170</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4962</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564437</v>
+        <v>564783</v>
       </c>
       <c r="R17" t="n">
-        <v>6968844</v>
+        <v>6968905</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119787440</v>
+        <v>119786568</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2369,34 +2238,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564783</v>
+        <v>564693</v>
       </c>
       <c r="R18" t="n">
-        <v>6968905</v>
+        <v>6968816</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119786568</v>
+        <v>119786607</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2495,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564693</v>
+        <v>564703</v>
       </c>
       <c r="R19" t="n">
-        <v>6968816</v>
+        <v>6968818</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,15 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119787703</v>
+        <v>119786557</v>
       </c>
       <c r="B20" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2573,34 +2432,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564690</v>
+        <v>564694</v>
       </c>
       <c r="R20" t="n">
-        <v>6968887</v>
+        <v>6968815</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,15 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119786557</v>
+        <v>119786761</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2675,34 +2529,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lungsjön, Lungsjön, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564694</v>
+        <v>564701</v>
       </c>
       <c r="R21" t="n">
-        <v>6968815</v>
+        <v>6968836</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,50 +2615,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119787425</v>
+        <v>119786611</v>
       </c>
       <c r="B22" t="n">
-        <v>89247</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1596</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Lungsjön, Lungsjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564783</v>
+        <v>564703</v>
       </c>
       <c r="R22" t="n">
-        <v>6968906</v>
+        <v>6968818</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2860,108 +2709,6 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>119787104</v>
-      </c>
-      <c r="B23" t="n">
-        <v>91839</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>6055</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Spadskinn</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Stereopsis vitellina</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(S.Lundell) D.A.Reid</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Långmyran, Långmyran, Jmt</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>564767</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6968890</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Hällesjö</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50826-2023 artfynd.xlsx
+++ b/artfynd/A 50826-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119786605</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787425</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787032</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787319</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787011</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788406</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787125</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787703</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119786868</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787262</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787760</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787828</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788409</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787104</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788007</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787440</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119786568</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119786607</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119786557</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119786761</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,8 +2814,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119786611</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>